--- a/tests/reports/DentNova_Test_Cases.xlsx
+++ b/tests/reports/DentNova_Test_Cases.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Selenium Test Cases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Appium Test Cases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="API Test Cases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Security Test Cases" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Load Test Cases" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Unit Test Cases" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Integration Test Cases" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Traceability Matrix" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Selenium Test Cases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Appium Test Cases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="API Test Cases" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Security Test Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Load Test Cases" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Unit Test Cases" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Integration Test Cases" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Traceability Matrix" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +38,35 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -95,8 +123,38 @@
         <fgColor rgb="00374151"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -110,11 +168,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -154,6 +226,53 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -229,6 +348,244 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>DentNova E2E Test Execution Status Summary</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Summary'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Summary'!$B$5:$B$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Summary'!$C$5:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Suite Breakdown (Passed vs Not Executed)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Summary'!C15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Summary'!$B$16:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Summary'!$C$16:$C$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Summary'!D15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Summary'!$B$16:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Summary'!$D$16:$D$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Summary'!E15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Summary'!$B$16:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Summary'!$E$16:$E$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -520,6 +877,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="25" customHeight="1">
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>DentNova QA Execution Executive Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Execution Metric</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Count / Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Total Tests Configured</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Active Pass Rate (Executed)</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Overall Progress Coverage</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>14.89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Module Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Test Suite / Worksheet</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Total Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Selenium Test Cases</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>117</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Appium Test Cases</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>90</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>API Test Cases</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Security Test Cases</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Load Test Cases</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Unit Test Cases</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Integration Test Cases</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>46</v>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="n">
+        <v>67</v>
+      </c>
+      <c r="D23" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>383</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>450</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1299,7 +1948,11 @@
           <t>Error: 'Invalid login credentials'</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1326,7 +1979,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1371,7 +2028,11 @@
           <t>Error message displayed; stay on /auth</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1398,7 +2059,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1441,7 +2106,11 @@
           <t>HTML5 validation or custom error shown; no navigation</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1468,7 +2137,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1512,7 +2185,11 @@
           <t>Registration form with name/email/password shown</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1539,7 +2216,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1585,7 +2266,11 @@
           <t>Account created; redirected to profile setup or dashboard</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1612,7 +2297,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1655,7 +2344,11 @@
           <t>Error: 'Email already registered'</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1682,7 +2375,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1726,7 +2423,11 @@
           <t>Checklist item for length shows incomplete; submit blocked</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1753,7 +2454,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1797,7 +2502,11 @@
           <t>Uppercase checklist item shows incomplete</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1824,7 +2533,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1868,7 +2581,11 @@
           <t>Number checklist item shows incomplete</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1895,7 +2612,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1939,7 +2660,11 @@
           <t>Special character checklist item shows incomplete</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -1966,7 +2691,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2009,7 +2738,11 @@
           <t>Password toggles between masked and visible</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -2036,7 +2769,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2160,7 +2897,11 @@
           <t>Success message: 'OTP sent to your email'</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -2187,7 +2928,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2231,7 +2976,11 @@
           <t>Error: 'Email is not registered'</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -2258,7 +3007,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2302,7 +3055,11 @@
           <t>Error: 'Invalid OTP code'</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -2329,7 +3086,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2374,7 +3135,11 @@
           <t>Error: password strength requirements shown</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -2401,7 +3166,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2446,7 +3215,11 @@
           <t>Error: 'Passwords do not match'</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -2473,7 +3246,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2675,7 +3452,11 @@
           <t>Session cleared; redirected to / or /auth</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -2702,7 +3483,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2983,7 +3768,11 @@
           <t>Score card with risk level shows correct data</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3010,7 +3799,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3054,7 +3847,11 @@
           <t>Days until next visit shown</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3081,7 +3878,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3124,7 +3925,11 @@
           <t>URL changes to /assessment</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3151,7 +3956,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3194,7 +4003,11 @@
           <t>URL changes to /tooth-scan</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3221,7 +4034,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3264,7 +4081,11 @@
           <t>URL changes to /reminders</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3291,7 +4112,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3336,7 +4161,11 @@
           <t>Dark mode remains active</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3363,7 +4192,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3721,7 +4554,11 @@
           <t>Timer shows value less than 2:00</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3748,7 +4585,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3794,7 +4635,11 @@
           <t>Timer frozen at paused time</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3821,7 +4666,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3865,7 +4714,11 @@
           <t>Timer resets to 2:00</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3892,7 +4745,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3936,7 +4793,11 @@
           <t>brushed_today = true in DB</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -3963,7 +4824,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4084,7 +4949,11 @@
           <t>At least 3 answer options shown</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4111,7 +4980,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4156,7 +5029,11 @@
           <t>Progress updates from 1/13 to 2/13</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4183,7 +5060,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4227,7 +5108,11 @@
           <t>Q1 shows previously selected answer</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4254,7 +5139,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4298,7 +5187,11 @@
           <t>Submit blocked; all questions must be answered</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4325,7 +5218,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4369,7 +5266,11 @@
           <t>Redirected to /assessment-result with score</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4396,7 +5297,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4439,7 +5344,11 @@
           <t>Score 0-100 and risk label (Low/Medium/High) shown</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4466,7 +5375,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4510,7 +5423,11 @@
           <t>Score = 100; Risk = LOW</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4537,7 +5454,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4581,7 +5502,11 @@
           <t>Score &lt; 50; Risk = HIGH</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4608,7 +5533,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4652,7 +5581,11 @@
           <t>Past assessments listed by date</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4679,7 +5612,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4723,7 +5660,11 @@
           <t>New row inserted with correct score, risk, answers JSON</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4750,7 +5691,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4871,7 +5816,11 @@
           <t>Message or modal: 'Complete assessment first'</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4898,7 +5847,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4942,7 +5895,11 @@
           <t>Drag-and-drop zone with instructions visible</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -4969,7 +5926,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5013,7 +5974,11 @@
           <t>Image thumbnail rendered; Analyze button active</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5040,7 +6005,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5083,7 +6052,11 @@
           <t>Error: 'Unsupported file format'</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5110,7 +6083,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5155,7 +6132,11 @@
           <t>Gum health, cleanliness, inflammation scores displayed</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5182,7 +6163,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5226,7 +6211,11 @@
           <t>Row inserted with scores and base64 image</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5253,7 +6242,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5296,7 +6289,11 @@
           <t>Thumbnails of past scans listed by date</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5323,7 +6320,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5366,7 +6367,11 @@
           <t>File download initiated (PDF/HTML)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5393,7 +6398,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5594,7 +6603,11 @@
           <t>Reminder appears in list; row inserted in reminders table</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5621,7 +6634,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5666,7 +6683,11 @@
           <t>Reminder in list; row in DB</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5693,7 +6714,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5736,7 +6761,11 @@
           <t>Date picker input appears</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5763,7 +6792,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5807,7 +6840,11 @@
           <t>enabled = false in DB; toggle visually off</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5834,7 +6871,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5878,7 +6919,11 @@
           <t>enabled = true in DB; toggle visually on</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5905,7 +6950,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5949,7 +6998,11 @@
           <t>Reminder disappears from UI; row deleted in DB</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -5976,7 +7029,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -6019,7 +7076,11 @@
           <t>days = 'Mon,Wed,Fri' stored in DB</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -6046,7 +7107,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -6168,7 +7233,11 @@
           <t>Browser notification banner appears</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -6195,7 +7264,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -6474,7 +7547,11 @@
           <t>Visit appears in Upcoming section; row in visits table</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -6501,7 +7578,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6545,7 +7626,11 @@
           <t>Past visit correctly categorised</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -6572,7 +7657,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6616,7 +7705,11 @@
           <t>Visit moved to Past section correctly</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -6643,7 +7736,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6687,7 +7784,11 @@
           <t>Visit removed from UI and DB</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -6714,7 +7815,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -6758,7 +7863,11 @@
           <t>Countdown correct to today's date</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -6785,7 +7894,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6906,7 +8019,11 @@
           <t>At least 3 dental articles visible</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -6933,7 +8050,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6976,7 +8097,11 @@
           <t>Article detail page loads with full content</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7003,7 +8128,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -7046,7 +8175,11 @@
           <t>Facts section shows dental tips</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7073,7 +8206,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -7116,7 +8253,11 @@
           <t>Quiz section with question shown</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7143,7 +8284,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -7186,7 +8331,11 @@
           <t>Green highlight; explanation shown</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7213,7 +8362,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -7256,7 +8409,11 @@
           <t>Red highlight on wrong answer</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7283,7 +8440,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -7326,7 +8487,11 @@
           <t>Video player loads or external link opens</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7353,7 +8518,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -7476,7 +8645,11 @@
           <t>users.name updated; success message shown</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7503,7 +8676,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -7547,7 +8724,11 @@
           <t>users.age updated</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7574,7 +8755,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -7618,7 +8803,11 @@
           <t>Validation error; save blocked</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7645,7 +8834,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -7689,7 +8882,11 @@
           <t>users.gender updated</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7716,7 +8913,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -7759,7 +8960,11 @@
           <t>Streak count shown</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7786,7 +8991,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7908,7 +9117,11 @@
           <t>Theme switches between dark and light</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -7935,7 +9148,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7979,7 +9196,11 @@
           <t>Current and new password fields visible</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8006,7 +9227,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -8051,7 +9276,11 @@
           <t>Row inserted into feedback table; success message</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8078,7 +9307,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -8121,7 +9354,11 @@
           <t>Modal with privacy policy text shown</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8148,7 +9385,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -8191,7 +9432,11 @@
           <t>Session cleared; redirected to /auth or /</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8218,7 +9463,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -8577,7 +9826,11 @@
           <t>Redirected to / or 404 page shown</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8604,7 +9857,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -8649,7 +9906,11 @@
           <t>Auth page uses dark color scheme</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8676,7 +9937,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -8720,7 +9985,11 @@
           <t>URL = /dashboard</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8747,7 +10016,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -8790,7 +10063,11 @@
           <t>URL = /reminders</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8817,7 +10094,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -8860,7 +10141,11 @@
           <t>URL = /education</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8887,7 +10172,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -8930,7 +10219,11 @@
           <t>URL = /profile</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -8957,7 +10250,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -9000,7 +10297,11 @@
           <t>URL = /settings</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9027,7 +10328,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -9071,7 +10376,11 @@
           <t>Browser navigates to previous page or home</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9098,7 +10407,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P117" s="2" t="inlineStr"/>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -9142,7 +10455,11 @@
           <t>Title includes 'DentNova' and page name</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9169,7 +10486,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -9212,7 +10533,11 @@
           <t>Favicon link tag present</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9239,7 +10564,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -9282,7 +10611,11 @@
           <t>Meta description tag present</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9309,7 +10642,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -9352,7 +10689,11 @@
           <t>Handled gracefully; no blank page</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9379,7 +10720,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -9423,7 +10768,11 @@
           <t>Feedback textarea visible</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9450,7 +10799,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -9494,7 +10847,11 @@
           <t>Success message; row in feedback table</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9521,7 +10878,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -9564,7 +10925,11 @@
           <t>Validation error; submission blocked</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9591,7 +10956,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -9635,7 +11004,11 @@
           <t>New assessment row added; history updated</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9662,7 +11035,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -9705,7 +11082,11 @@
           <t>Result page shows last assessment data</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9732,7 +11113,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -9776,7 +11161,11 @@
           <t>Streak shows 0 or 'Start your streak!'</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9803,7 +11192,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -9846,7 +11239,11 @@
           <t>Message shown: 'No upcoming visit' or similar</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9873,7 +11270,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -9916,7 +11317,11 @@
           <t>Error: 'Please upload an image first'</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -9943,7 +11348,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P129" s="2" t="inlineStr"/>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -9986,7 +11395,11 @@
           <t>Error or auto-resize without crash</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10013,7 +11426,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P130" s="2" t="inlineStr"/>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -10056,7 +11473,11 @@
           <t>Empty state message shown</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10083,7 +11504,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P131" s="2" t="inlineStr"/>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -10127,7 +11552,11 @@
           <t>Overdue badge or indicator shown</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10154,7 +11583,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -10197,7 +11630,11 @@
           <t>Empty state: 'No upcoming visits scheduled'</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10224,7 +11661,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P133" s="2" t="inlineStr"/>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -10268,7 +11709,11 @@
           <t>Visits listed nearest date first</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10295,7 +11740,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P134" s="2" t="inlineStr"/>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -10338,7 +11787,11 @@
           <t>Articles filter by keyword</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10365,7 +11818,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P135" s="2" t="inlineStr"/>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -10410,7 +11867,11 @@
           <t>Photo shown in circular frame; photo_url updated in DB</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10437,7 +11898,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -10482,7 +11947,11 @@
           <t>Success message; password updated in Supabase and Firebase</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10509,7 +11978,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P137" s="2" t="inlineStr"/>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -10553,7 +12026,11 @@
           <t>Error: 'Current password incorrect'</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10580,7 +12057,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P138" s="2" t="inlineStr"/>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -10624,7 +12105,11 @@
           <t>users.name populated after registration</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10651,7 +12136,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -10695,7 +12184,11 @@
           <t>Validation error or truncation; no crash</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10722,7 +12215,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -10766,7 +12263,11 @@
           <t>Registration succeeds if other rules met</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10793,7 +12294,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P141" s="2" t="inlineStr"/>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -10836,7 +12341,11 @@
           <t>Image preview shown; Analyze button active</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10863,7 +12372,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P142" s="2" t="inlineStr"/>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -10908,7 +12421,11 @@
           <t>Answer retained (localStorage or session)</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -10935,7 +12452,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P143" s="2" t="inlineStr"/>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -10978,7 +12499,11 @@
           <t>Brushing timer card or link present</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11005,7 +12530,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P144" s="2" t="inlineStr"/>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -11048,7 +12577,11 @@
           <t>Flossing card present with log button</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11075,7 +12608,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P145" s="2" t="inlineStr"/>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -11119,7 +12656,11 @@
           <t>Visit shows clinic and optional note</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11146,7 +12687,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P146" s="2" t="inlineStr"/>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -11190,7 +12735,11 @@
           <t>users.concerns field updated</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11217,7 +12766,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P147" s="2" t="inlineStr"/>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -11262,7 +12815,11 @@
           <t>Session established; redirected to /dashboard</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11289,7 +12846,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P148" s="2" t="inlineStr"/>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -11334,7 +12895,11 @@
           <t>User still logged in without re-entering credentials</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11361,7 +12926,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P149" s="2" t="inlineStr"/>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -11404,7 +12973,11 @@
           <t>Each click shows a new dental fact</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11431,7 +13004,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P150" s="2" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -11474,7 +13051,11 @@
           <t>Label is consistent with score range</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local React web server at http://localhost:5174 not running</t>
+        </is>
+      </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11501,14 +13082,18 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P151" s="2" t="inlineStr"/>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>Requires local web app development server active at http://localhost:5174</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11659,7 +13244,11 @@
           <t>SplashActivity visible for ~2 seconds</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11686,7 +13275,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -11729,7 +13322,11 @@
           <t>Transitions to AuthActivity</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11756,7 +13353,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -11800,7 +13401,11 @@
           <t>Onboarding page 2 appears</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11827,7 +13432,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -11870,7 +13479,11 @@
           <t>Navigates to AuthActivity</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11897,7 +13510,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -11940,7 +13557,11 @@
           <t>Both fields visible and enabled</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -11967,7 +13588,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -12012,7 +13637,11 @@
           <t>HomeActivity opened</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12039,7 +13668,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -12083,7 +13716,11 @@
           <t>Toast/error: 'Invalid credentials'</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12110,7 +13747,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -12154,7 +13795,11 @@
           <t>Validation message shown</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12181,7 +13826,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -12224,7 +13873,11 @@
           <t>Password text toggled</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12251,7 +13904,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -12294,7 +13951,11 @@
           <t>Google button visible and tappable</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12321,7 +13982,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -12364,7 +14029,11 @@
           <t>Registration form appears</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12391,7 +14060,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -12435,7 +14108,11 @@
           <t>Account created; redirect to profile or home</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12462,7 +14139,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -12506,7 +14187,11 @@
           <t>Validation error for password strength</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12533,7 +14218,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -12578,7 +14267,11 @@
           <t>OTP send confirmation shown</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12605,7 +14298,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -12648,7 +14345,11 @@
           <t>Navigates to reset password screen</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12675,7 +14376,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -12718,7 +14423,11 @@
           <t>Opens HomeActivity; no login required</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12745,7 +14454,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -12789,7 +14502,11 @@
           <t>AuthActivity shown after logout</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12816,7 +14533,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -12859,7 +14580,11 @@
           <t>All home widgets rendered</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12886,7 +14611,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -12929,7 +14658,11 @@
           <t>Streak number matches DB value</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -12956,7 +14689,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -12999,7 +14736,11 @@
           <t>Both habit cards visible</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13026,7 +14767,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -13069,7 +14814,11 @@
           <t>AssessmentActivity launched</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13096,7 +14845,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -13139,7 +14892,11 @@
           <t>ToothScanActivity launched</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13166,7 +14923,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -13209,7 +14970,11 @@
           <t>AssessmentActivity shows Q1</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13236,7 +15001,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -13279,7 +15048,11 @@
           <t>Next button becomes enabled</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13306,7 +15079,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -13350,7 +15127,11 @@
           <t>Progress bar reflects 2/13</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13377,7 +15158,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -13420,7 +15205,11 @@
           <t>AssessmentResultActivity shows score</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13447,7 +15236,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -13490,7 +15283,11 @@
           <t>Row with score and risk present</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13517,7 +15314,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -13560,7 +15361,11 @@
           <t>ToothScanActivity visible</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13587,7 +15392,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -13631,7 +15440,11 @@
           <t>Device camera app launched</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13658,7 +15471,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -13701,7 +15518,11 @@
           <t>Gallery picker opens</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13728,7 +15549,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -13772,7 +15597,11 @@
           <t>Scores displayed: plaque, gum, cleanliness</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13799,7 +15628,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -13842,7 +15675,11 @@
           <t>Row with scores and image_base64 inserted</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13869,7 +15706,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -13912,7 +15753,11 @@
           <t>Timer screen shows 2:00</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -13939,7 +15784,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -13983,7 +15832,11 @@
           <t>Timer decremented below 2:00</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14010,7 +15863,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -14053,7 +15910,11 @@
           <t>brushed_today = true; success animation shown</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14080,7 +15941,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -14123,7 +15988,11 @@
           <t>Reminders list shown with Add button</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14150,7 +16019,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -14195,7 +16068,11 @@
           <t>Reminder appears in list; DB row created</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14222,7 +16099,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -14265,7 +16146,11 @@
           <t>enabled field toggled in DB; alarm updated</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14292,7 +16177,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -14335,7 +16224,11 @@
           <t>Reminder removed from list and DB</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14362,7 +16255,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -14405,7 +16302,11 @@
           <t>System notification appears with reminder title</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14432,7 +16333,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -14476,7 +16381,11 @@
           <t>BootReceiver re-registers alarms</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14503,7 +16412,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -14546,7 +16459,11 @@
           <t>Visit list with upcoming/past sections shown</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14573,7 +16490,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -14616,7 +16537,11 @@
           <t>Visit in Upcoming section; DB row created</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14643,7 +16568,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -14687,7 +16616,11 @@
           <t>Past visit correctly categorised</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14714,7 +16647,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -14757,7 +16694,11 @@
           <t>Article list visible</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14784,7 +16725,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -14827,7 +16772,11 @@
           <t>ArticleDetailActivity shows full content</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14854,7 +16803,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -14897,7 +16850,11 @@
           <t>Quiz screen with first question shown</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14924,7 +16881,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -14967,7 +16928,11 @@
           <t>Green highlight; explanation shown</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -14994,7 +16959,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -15037,7 +17006,11 @@
           <t>Video plays or external app opens</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15064,7 +17037,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -15107,7 +17084,11 @@
           <t>Name, age, gender fields populated</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15134,7 +17115,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -15178,7 +17163,11 @@
           <t>users.name updated in DB; toast shown</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15205,7 +17194,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -15248,7 +17241,11 @@
           <t>Settings screen with options shown</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15275,7 +17272,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -15318,7 +17319,11 @@
           <t>App theme switches; persists on restart</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15345,7 +17350,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -15390,7 +17399,11 @@
           <t>feedback table row inserted</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15417,7 +17430,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -15460,7 +17477,11 @@
           <t>Session cleared; AuthActivity shown</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15487,7 +17508,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -15531,7 +17556,11 @@
           <t>Error: 'No internet connection'</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15558,7 +17587,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -15602,7 +17635,11 @@
           <t>Dashboard shows last-cached data without crash</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15629,7 +17666,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -15673,7 +17714,11 @@
           <t>Fresh data fetched from Supabase</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15700,7 +17745,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -15743,7 +17792,11 @@
           <t>Activity recreates; no crash; data retained</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15770,7 +17823,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -15813,7 +17870,11 @@
           <t>Normal layout restored</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15840,7 +17901,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -15884,7 +17949,11 @@
           <t>SplashActivity shown within 3000ms</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15911,7 +17980,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -15954,7 +18027,11 @@
           <t>Less than 2000ms</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -15981,7 +18058,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -16024,7 +18105,11 @@
           <t>List visible within 1000ms</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16051,7 +18136,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -16094,7 +18183,11 @@
           <t>Q1 visible within 1000ms</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16121,7 +18214,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -16165,7 +18262,11 @@
           <t>Heap stays &lt; 150MB; no significant leak</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16192,7 +18293,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -16236,7 +18341,11 @@
           <t>All interactive elements announced correctly</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16263,7 +18372,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -16306,7 +18419,11 @@
           <t>All buttons &gt;= 48dp height and width</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16333,7 +18450,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -16377,7 +18498,11 @@
           <t>No text cut off; no layout overflow</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16404,7 +18529,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -16447,7 +18576,11 @@
           <t>WCAG AA contrast ratio met for all primary text</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16474,7 +18607,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -16517,7 +18654,11 @@
           <t>Warning shown or sensitive features restricted</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16544,7 +18685,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -16588,7 +18733,11 @@
           <t>No email or password text visible in Logcat</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16615,7 +18764,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -16658,7 +18811,11 @@
           <t>No password key in preferences file</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16685,7 +18842,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -16729,7 +18890,11 @@
           <t>All URLs use HTTPS protocol</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16756,7 +18921,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -16800,7 +18969,11 @@
           <t>No JWT token visible in Logcat</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16827,7 +19000,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -16871,7 +19048,11 @@
           <t>Validation error or minimum age enforced</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16898,7 +19079,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -16942,7 +19127,11 @@
           <t>Validation error; max age exceeded</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -16969,7 +19158,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -17013,7 +19206,11 @@
           <t>Toast error: 'Name cannot be empty'</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17040,7 +19237,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -17084,7 +19285,11 @@
           <t>Name saved correctly with special chars</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17111,7 +19316,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -17155,7 +19364,11 @@
           <t>time column = '08:30'</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17182,7 +19395,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -17225,7 +19442,11 @@
           <t>Past dates grayed out or rejected</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17252,7 +19473,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -17295,7 +19520,11 @@
           <t>Channel 'DentNova Reminders' visible in Settings</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17322,7 +19551,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -17365,7 +19598,11 @@
           <t>App opens and shows RemindersActivity</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17392,7 +19629,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -17435,7 +19676,11 @@
           <t>Notification removed; no reappearance</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17462,7 +19707,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -17505,7 +19754,11 @@
           <t>AssessmentActivity launched directly</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17532,7 +19785,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -17575,7 +19832,11 @@
           <t>ToothScanActivity launched directly</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17602,7 +19863,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -17647,7 +19912,11 @@
           <t>All previous preferences cleared; fresh state</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17674,7 +19943,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -17717,7 +19990,11 @@
           <t>OnboardingActivity shown on first launch</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17744,7 +20021,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -17788,7 +20069,11 @@
           <t>All UI labels in English</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17815,7 +20100,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -17859,7 +20148,11 @@
           <t>No text cutoff; ellipsis used where appropriate</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17886,7 +20179,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -17930,7 +20227,11 @@
           <t>No unnecessary wakelock held</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Appium server and Android emulator not active</t>
+        </is>
+      </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -17957,14 +20258,18 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Appium server on port 4723 and running Android emulator with DentNova APK installed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18427,7 +20732,11 @@
           <t>HTTP 200; OTP email sent</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -18454,7 +20763,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -18497,7 +20810,11 @@
           <t>HTTP 400; validation error</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -18524,7 +20841,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -18567,7 +20888,11 @@
           <t>HTTP 429; 'Too many requests' in message</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -18594,7 +20919,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -18638,7 +20967,11 @@
           <t>HTTP 200; OTP sent successfully</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -18665,7 +20998,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -18786,7 +21123,11 @@
           <t>HTTP 400; 'Invalid OTP code'</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -18813,7 +21154,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -18856,7 +21201,11 @@
           <t>HTTP 400; 'OTP has expired'</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -18883,7 +21232,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -18926,7 +21279,11 @@
           <t>HTTP 400; 'already been used'</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -18953,7 +21310,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -18996,7 +21357,11 @@
           <t>HTTP 200; 'OTP verified successfully'</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19023,7 +21388,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -19144,7 +21513,11 @@
           <t>HTTP 400; OTP validation failed</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19171,7 +21544,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -19214,7 +21591,11 @@
           <t>HTTP 200; password updated in Supabase and Firebase</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19241,7 +21622,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -19440,7 +21825,11 @@
           <t>JSON with inflammation_score, cleanliness_score, overall_score, result_label</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19467,7 +21856,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -19510,7 +21903,11 @@
           <t>HTTP 400 or 415; error message</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19537,7 +21934,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -19580,7 +21981,11 @@
           <t>JSON with risk_score or risk_level</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19607,7 +22012,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -19650,7 +22059,11 @@
           <t>HTTP 400; missing field error</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19677,7 +22090,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -19798,7 +22215,11 @@
           <t>HTTP 200; access_token returned</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19825,7 +22246,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -19868,7 +22293,11 @@
           <t>HTTP 400; 'Invalid login credentials'</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19895,7 +22324,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -19938,7 +22371,11 @@
           <t>HTTP 200; JSON array of users</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -19965,7 +22402,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -20008,7 +22449,11 @@
           <t>HTTP 200; reminders array for current user</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20035,7 +22480,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -20078,7 +22527,11 @@
           <t>HTTP 200; visits array</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20105,7 +22558,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -20148,7 +22605,11 @@
           <t>HTTP 201; reminder row created</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20175,7 +22636,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -20218,7 +22683,11 @@
           <t>HTTP 200 or 204; row deleted</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20245,7 +22714,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -20288,7 +22761,11 @@
           <t>HTTP 201; assessment row created</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20315,7 +22792,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -20358,7 +22839,11 @@
           <t>Empty array or 403; RLS blocks cross-user access</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20385,7 +22870,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -20428,7 +22917,11 @@
           <t>HTTP 201; row inserted</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20455,7 +22948,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -20498,7 +22995,11 @@
           <t>HTTP 201; scan record created</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20525,7 +23026,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -20880,7 +23385,11 @@
           <t>All expected columns present</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20907,7 +23416,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -20951,7 +23464,11 @@
           <t>CORS header present in response</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -20978,7 +23495,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -21022,7 +23543,11 @@
           <t>HTTP 500; 'Failed to send OTP' in message</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21049,7 +23574,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -21092,7 +23621,11 @@
           <t>HTTP 200 or 204; name and age updated</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21119,7 +23652,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -21162,7 +23699,11 @@
           <t>HTTP 200 or 201; no duplicate rows</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21189,7 +23730,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -21233,7 +23778,11 @@
           <t>Each score: 0 &lt;= score &lt;= 100</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21260,7 +23809,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -21304,7 +23857,11 @@
           <t>risk_score is numeric 0-100</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21331,7 +23888,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -21375,7 +23936,11 @@
           <t>otp_hash present; OTP email contains 6-digit code</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21402,7 +23967,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -21445,7 +24014,11 @@
           <t>Columns: id, message, created_at present</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21472,7 +24045,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -21515,7 +24092,11 @@
           <t>Empty array returned; RLS blocks access</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21542,7 +24123,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -21585,7 +24170,11 @@
           <t>Empty array returned</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21612,7 +24201,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -21655,7 +24248,11 @@
           <t>Only one OTP stored; no DB deadlock; one 200, others 429</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21682,7 +24279,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -21726,7 +24327,11 @@
           <t>expires_in = 3600 (1 hour) or configured value</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21753,7 +24358,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -21796,7 +24405,11 @@
           <t>HTTP 200; new access_token returned</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -21823,14 +24436,18 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21981,7 +24598,11 @@
           <t>No SQL error; login rejected normally</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22008,7 +24629,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -22052,7 +24677,11 @@
           <t>Tag stored as literal text; no alert fired</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22079,7 +24708,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -22123,7 +24756,11 @@
           <t>Payload rendered as escaped text</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22150,7 +24787,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -22193,7 +24834,11 @@
           <t>Empty array or 403 returned</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22220,7 +24865,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -22263,7 +24912,11 @@
           <t>Empty array; no cross-user data leak</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22290,7 +24943,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -22333,7 +24990,11 @@
           <t>HTTP 403 or 0 rows affected</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22360,7 +25021,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -22403,7 +25068,11 @@
           <t>HTTP 401 or 403</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22430,7 +25099,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -22473,7 +25146,11 @@
           <t>Account locked or rate limiting engaged</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22500,7 +25177,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -22543,7 +25224,11 @@
           <t>HTTP 429 on 4th request</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22570,7 +25255,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -22614,7 +25303,11 @@
           <t>X-Frame-Options header present</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22641,7 +25334,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -22684,7 +25381,11 @@
           <t>X-Content-Type-Options: nosniff present</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22711,7 +25412,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -22754,7 +25459,11 @@
           <t>CSP header present and configured</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22781,7 +25490,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -22824,7 +25537,11 @@
           <t>Strict-Transport-Security header present</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22851,7 +25568,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -22895,7 +25616,11 @@
           <t>Password stored as bcrypt hash</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22922,7 +25647,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -22966,7 +25695,11 @@
           <t>301/302 redirect to HTTPS</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -22993,7 +25726,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -23036,7 +25773,11 @@
           <t>HTTP 401; token invalid</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23063,7 +25804,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -23108,7 +25853,11 @@
           <t>New token issued after authentication</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23135,7 +25884,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -23178,7 +25931,11 @@
           <t>HTTP 413 or 400; no crash</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23205,7 +25962,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -23248,7 +26009,11 @@
           <t>CORS headers restrict unauthorised origin</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23275,7 +26040,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -23319,7 +26088,11 @@
           <t>otp_hash field is SHA-256 hash, not the raw OTP</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23346,7 +26119,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -23389,7 +26166,11 @@
           <t>HTTP 429 or 403; account temporarily locked</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23416,7 +26197,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -23460,7 +26245,11 @@
           <t>OTP not visible in browser address bar</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23487,7 +26276,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -23531,7 +26324,11 @@
           <t>No 'password' or 'encrypted_password' field in response</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23558,7 +26355,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -23602,7 +26403,11 @@
           <t>anon key is in bundle (acceptable) but not in API responses</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23629,7 +26434,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -23673,7 +26482,11 @@
           <t>Only MainActivity/SplashActivity exported; others require permission</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23700,7 +26513,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -23744,7 +26561,11 @@
           <t>debuggable=false in release manifest</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23771,7 +26592,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -23814,7 +26639,11 @@
           <t>Email header injection not executed; 400 returned</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23841,7 +26670,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -23885,7 +26718,11 @@
           <t>Session cookies have Secure=true and HttpOnly=true</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23912,7 +26749,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -23956,7 +26797,11 @@
           <t>No access token in Referer headers to external domains</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -23983,7 +26828,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -24027,7 +26876,11 @@
           <t>Request fails or field is ignored; no privilege escalation</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: local OWASP ZAP daemon not reachable at http://localhost:8080</t>
+        </is>
+      </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -24054,14 +26907,18 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Requires active local OWASP ZAP daemon listener configured on port 8080</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25635,7 +28492,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29892,7 +32749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30360,7 +33217,11 @@
           <t>Reminder appears in Android RemindersActivity</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -30387,7 +33248,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -30431,7 +33296,11 @@
           <t>Reminder appears on Web /reminders</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -30458,7 +33327,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -30502,7 +33375,11 @@
           <t>Visit appears in Android upcoming list</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -30529,7 +33406,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -30573,7 +33454,11 @@
           <t>Visit appears on Web upcoming section</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -30600,7 +33485,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -30644,7 +33533,11 @@
           <t>brushed_today=true on Android dashboard card</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -30671,7 +33564,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -30715,7 +33612,11 @@
           <t>Flossing card shows completed on Web</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -30742,7 +33643,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -30786,7 +33691,11 @@
           <t>Android dashboard shows updated score</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -30813,7 +33722,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -30856,7 +33769,11 @@
           <t>Both show identical streak count</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -30883,7 +33800,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -30927,7 +33848,11 @@
           <t>Scan result listed on Android</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -30954,7 +33879,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -30998,7 +33927,11 @@
           <t>Web profile shows updated name</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31025,7 +33958,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -31068,7 +34005,11 @@
           <t>HTTP 201; row in feedback table</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31095,7 +34036,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -31139,7 +34084,11 @@
           <t>Reminder no longer in Android list</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31166,7 +34115,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -31210,7 +34163,11 @@
           <t>Date shown correctly in expected format</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31237,7 +34194,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -31283,7 +34244,11 @@
           <t>User can login with new password; old password fails</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31310,7 +34275,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -31355,7 +34324,11 @@
           <t>DB score matches what was shown on result page</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31382,7 +34355,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -31426,7 +34403,11 @@
           <t>Token refreshed automatically; call succeeds</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31453,7 +34434,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -31499,7 +34484,11 @@
           <t>User registered; assessment row saved; scan row saved; all scores visible</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31526,7 +34515,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -31573,7 +34566,11 @@
           <t>Dashboard loaded; reminder row inserted with correct user_id</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31600,7 +34597,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -31646,7 +34647,11 @@
           <t>streak_count incremented; last_habit_date = today</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31673,7 +34678,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -31719,7 +34728,11 @@
           <t>Full OTP flow completes; login succeeds with new password</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31746,7 +34759,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -31791,7 +34808,11 @@
           <t>Dashboard shows 'Visit in 7 days'</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31818,7 +34839,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -31862,7 +34887,11 @@
           <t>Streak count unchanged; no duplicate increment</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31889,7 +34918,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -31933,7 +34966,11 @@
           <t>DB score == expected score from answer calculation</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -31960,7 +34997,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -32004,7 +35045,11 @@
           <t>enabled = true in DB; no NULL state</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32031,7 +35076,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -32075,7 +35124,11 @@
           <t>All scores &gt;= 0</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32102,7 +35155,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -32145,7 +35202,11 @@
           <t>All user_ids unique; no collision in test dataset</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32172,7 +35233,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -32216,7 +35281,11 @@
           <t>All sections render without errors</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32243,7 +35312,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -32287,7 +35360,11 @@
           <t>Login form renders without CSS issues</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32314,7 +35391,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -32358,7 +35439,11 @@
           <t>Dashboard renders without layout issues</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32385,7 +35470,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -32429,7 +35518,11 @@
           <t>Reminders page renders correctly</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32456,7 +35549,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -32501,7 +35598,11 @@
           <t>Login succeeds; dashboard loads on mobile Chrome</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32528,7 +35629,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -32572,7 +35677,11 @@
           <t>Old password rejected; new password accepted</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32599,7 +35708,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -32644,7 +35757,11 @@
           <t>Progress retained; user not sent back to Q1</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32671,7 +35788,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -32715,7 +35836,11 @@
           <t>Deleted visit does not appear</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32742,7 +35867,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -32787,7 +35916,11 @@
           <t>Toggle shows disabled; enabled=false in DB</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32814,7 +35947,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -32859,7 +35996,11 @@
           <t>Exactly 2 rows with different created_at timestamps</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32886,7 +36027,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -32931,7 +36076,11 @@
           <t>streak_count still 5 after profile edit</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -32958,7 +36107,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -33002,7 +36155,11 @@
           <t>History shows 3 entries in descending date order</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -33029,7 +36186,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -33073,7 +36234,11 @@
           <t>Redirected to /auth</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -33100,7 +36265,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -33144,7 +36313,11 @@
           <t>Newest scan shown first</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -33171,7 +36344,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -33215,7 +36392,11 @@
           <t>streak_count = 0</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -33242,7 +36423,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -33286,7 +36471,11 @@
           <t>3 reminder cards shown; data matches DB</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -33313,7 +36502,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -33357,7 +36550,11 @@
           <t>Visits correctly split by section</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -33384,7 +36581,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -33428,7 +36629,11 @@
           <t>User-friendly error (not raw Supabase error) shown</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -33455,7 +36660,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -33499,7 +36708,11 @@
           <t>Toast or dialog: 'Session expired, please login again'</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -33526,7 +36739,11 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -33570,7 +36787,11 @@
           <t>Toast: 'Analysis failed, please try again'</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Skipped: Dependency backend or environment variable not fully configured on local host</t>
+        </is>
+      </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>NOT EXECUTED</t>
@@ -33597,14 +36818,18 @@
           <t>DentNova QA Team</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Requires active Supabase database keys or active ML/OTP production environment variables</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/tests/reports/DentNova_Test_Cases.xlsx
+++ b/tests/reports/DentNova_Test_Cases.xlsx
@@ -7,15 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Selenium Test Cases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Appium Test Cases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="API Test Cases" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Security Test Cases" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Load Test Cases" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Unit Test Cases" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Integration Test Cases" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Traceability Matrix" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Selenium Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Appium Test Cases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="API Test Cases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security Test Cases" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Load Test Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Unit Test Cases" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Integration Test Cases" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Traceability Matrix" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,35 +37,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000284C7"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="14"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -123,38 +95,8 @@
         <fgColor rgb="00374151"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E8F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -168,25 +110,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -226,53 +154,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -348,244 +229,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>DentNova E2E Test Execution Status Summary</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Summary'!C4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Summary'!$B$5:$B$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Summary'!$C$5:$C$7</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Suite Breakdown (Passed vs Not Executed)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Summary'!C15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Summary'!$B$16:$B$22</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Summary'!$C$16:$C$22</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Summary'!D15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Summary'!$B$16:$B$22</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Summary'!$D$16:$D$22</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Summary'!E15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Summary'!$B$16:$B$22</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Summary'!$E$16:$E$22</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5760000" cy="3960000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7200000" cy="4320000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -877,298 +520,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="25" customHeight="1">
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>DentNova QA Execution Executive Dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Execution Metric</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Count / Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Total Tests Configured</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="n">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Active Pass Rate (Executed)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Overall Progress Coverage</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>14.89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Module Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>Test Suite / Worksheet</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>Total Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>Selenium Test Cases</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="n">
-        <v>33</v>
-      </c>
-      <c r="D16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>117</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>Appium Test Cases</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>90</v>
-      </c>
-      <c r="F17" s="21" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>API Test Cases</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>39</v>
-      </c>
-      <c r="F18" s="21" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>Security Test Cases</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="F19" s="21" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>Load Test Cases</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="D20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="F20" s="21" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>Unit Test Cases</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="n">
-        <v>10</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="25" t="n">
-        <v>48</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>Integration Test Cases</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="25" t="n">
-        <v>46</v>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="n">
-        <v>67</v>
-      </c>
-      <c r="D23" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="29" t="n">
-        <v>383</v>
-      </c>
-      <c r="F23" s="30" t="n">
-        <v>450</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:P151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1341,7 +692,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -1420,7 +771,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -1499,7 +850,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -1578,7 +929,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1657,7 +1008,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1736,7 +1087,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1815,7 +1166,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1895,7 +1246,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -2844,7 +2195,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -3321,7 +2672,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3400,7 +2751,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3558,7 +2909,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3637,7 +2988,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3716,7 +3067,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4267,7 +3618,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4345,7 +3696,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4423,7 +3774,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4501,7 +3852,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -4898,7 +4249,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5765,7 +5116,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -6472,7 +5823,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -6550,7 +5901,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -7181,7 +6532,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -7338,7 +6689,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -7416,7 +6767,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -7494,7 +6845,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -7968,7 +7319,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -8592,7 +7943,7 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -9065,7 +8416,7 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
@@ -9538,7 +8889,7 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
@@ -9617,7 +8968,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
@@ -9696,7 +9047,7 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
@@ -9775,7 +9126,7 @@
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
@@ -13093,7 +12444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20269,7 +19620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20446,7 +19797,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -20525,7 +19876,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -20603,7 +19954,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -20681,7 +20032,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -21072,7 +20423,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -21462,7 +20813,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -21696,7 +21047,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -21774,7 +21125,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -22164,7 +21515,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -23100,7 +22451,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -23178,7 +22529,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -23256,7 +22607,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -23334,7 +22685,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -24447,7 +23798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26918,7 +26269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27097,7 +26448,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -27175,7 +26526,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -27253,7 +26604,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -27331,7 +26682,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -27410,7 +26761,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -27488,7 +26839,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -27916,7 +27267,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -28492,7 +27843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28669,7 +28020,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -28747,7 +28098,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -28825,7 +28176,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -28903,7 +28254,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -28981,7 +28332,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -29619,7 +28970,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -29697,7 +29048,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -29775,7 +29126,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -29853,7 +29204,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -30281,7 +29632,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -32749,7 +32100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32928,7 +32279,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -33007,7 +32358,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -33086,7 +32437,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -33165,7 +32516,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -36829,7 +36180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
